--- a/artfynd/A 55280-2025 artfynd.xlsx
+++ b/artfynd/A 55280-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,3805 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129976313</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>574432</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6738763</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129976312</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>574624</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6738804</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129978658</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>574591</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6738884</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129978662</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>574596</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6738880</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129976308</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>574294</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6738677</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129978665</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>574442</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6738569</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129978657</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>574603</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6738892</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129978682</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92884</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>574307</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6738683</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129976309</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>574638</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6738853</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129976311</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>574666</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6738788</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129978648</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98828</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>574476</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6738614</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129978651</v>
+      </c>
+      <c r="B14" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>574626</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6738882</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129978664</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90984</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>574298</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6738745</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129976350</v>
+      </c>
+      <c r="B16" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>574629</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6738849</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129976307</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92922</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>574335</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6738615</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129976348</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>574433</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6738720</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129978649</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>574294</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6738742</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129978660</v>
+      </c>
+      <c r="B20" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>574590</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6738880</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129976353</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>574636</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6738816</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129978642</v>
+      </c>
+      <c r="B22" t="n">
+        <v>83055</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>574606</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6738867</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129978652</v>
+      </c>
+      <c r="B23" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>574634</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6738899</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129978681</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98711</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>574342</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6738765</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129976315</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>574651</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6738821</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129978653</v>
+      </c>
+      <c r="B26" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>574629</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6738896</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129978646</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97665</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>574420</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6738737</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129976310</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>574679</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6738793</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129978641</v>
+      </c>
+      <c r="B29" t="n">
+        <v>83055</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>574386</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6738787</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129978650</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>574540</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6738742</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129978645</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98712</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>574565</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6738840</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129976317</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78750</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>353</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>574617</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6738757</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129976316</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>574581</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6738833</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129976349</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>574623</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6738796</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129976351</v>
+      </c>
+      <c r="B35" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>574632</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6738902</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129978643</v>
+      </c>
+      <c r="B36" t="n">
+        <v>83055</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>574627</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6738915</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129976314</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kitteln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>574635</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6738811</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129978654</v>
+      </c>
+      <c r="B38" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>574600</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6738914</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129978656</v>
+      </c>
+      <c r="B39" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>574604</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6738899</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129978663</v>
+      </c>
+      <c r="B40" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sneåsen söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>574595</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6738867</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55280-2025 artfynd.xlsx
+++ b/artfynd/A 55280-2025 artfynd.xlsx
@@ -782,45 +782,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129976313</v>
+        <v>129976312</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574432</v>
+        <v>574624</v>
       </c>
       <c r="R3" t="n">
-        <v>6738763</v>
+        <v>6738804</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +873,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,60 +892,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129976312</v>
+        <v>129978662</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>75196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574624</v>
+        <v>574596</v>
       </c>
       <c r="R4" t="n">
-        <v>6738804</v>
+        <v>6738880</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,19 +971,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1086,48 +1086,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129978662</v>
+        <v>129976313</v>
       </c>
       <c r="B6" t="n">
-        <v>75196</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574596</v>
+        <v>574432</v>
       </c>
       <c r="R6" t="n">
-        <v>6738880</v>
+        <v>6738763</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,22 +1171,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129976308</v>
+        <v>129978665</v>
       </c>
       <c r="B7" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,37 +1194,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574294</v>
+        <v>574442</v>
       </c>
       <c r="R7" t="n">
-        <v>6738677</v>
+        <v>6738569</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,22 +1268,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129978665</v>
+        <v>129976308</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,37 +1291,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574442</v>
+        <v>574294</v>
       </c>
       <c r="R8" t="n">
-        <v>6738569</v>
+        <v>6738677</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1365,12 +1365,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1685,60 +1685,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129976311</v>
+        <v>129978651</v>
       </c>
       <c r="B12" t="n">
-        <v>98794</v>
+        <v>75196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574666</v>
+        <v>574626</v>
       </c>
       <c r="R12" t="n">
-        <v>6738788</v>
+        <v>6738882</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1776,29 +1764,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129978648</v>
+        <v>129978664</v>
       </c>
       <c r="B13" t="n">
-        <v>98828</v>
+        <v>90984</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1806,38 +1793,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>5685</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574476</v>
+        <v>574298</v>
       </c>
       <c r="R13" t="n">
-        <v>6738614</v>
+        <v>6738745</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1878,7 +1861,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1890,17 +1872,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Lena Thommson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129978651</v>
+        <v>129978648</v>
       </c>
       <c r="B14" t="n">
-        <v>75196</v>
+        <v>98828</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,34 +1890,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>219874</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574626</v>
+        <v>574476</v>
       </c>
       <c r="R14" t="n">
-        <v>6738882</v>
+        <v>6738614</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1976,6 +1962,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1987,55 +1974,67 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129978664</v>
+        <v>129976311</v>
       </c>
       <c r="B15" t="n">
-        <v>90984</v>
+        <v>98794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5685</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574298</v>
+        <v>574666</v>
       </c>
       <c r="R15" t="n">
-        <v>6738745</v>
+        <v>6738788</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2073,18 +2072,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2297,60 +2297,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129976348</v>
+        <v>129978649</v>
       </c>
       <c r="B18" t="n">
-        <v>98794</v>
+        <v>78841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574433</v>
+        <v>574294</v>
       </c>
       <c r="R18" t="n">
-        <v>6738720</v>
+        <v>6738742</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2388,51 +2376,50 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129978649</v>
+        <v>129978660</v>
       </c>
       <c r="B19" t="n">
-        <v>78841</v>
+        <v>75196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2442,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574294</v>
+        <v>574590</v>
       </c>
       <c r="R19" t="n">
-        <v>6738742</v>
+        <v>6738880</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2504,48 +2491,60 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129978660</v>
+        <v>129976348</v>
       </c>
       <c r="B20" t="n">
-        <v>75196</v>
+        <v>98794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574590</v>
+        <v>574433</v>
       </c>
       <c r="R20" t="n">
-        <v>6738880</v>
+        <v>6738720</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2583,28 +2582,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129976353</v>
+        <v>129978642</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>83055</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2612,37 +2612,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574636</v>
+        <v>574606</v>
       </c>
       <c r="R21" t="n">
-        <v>6738816</v>
+        <v>6738867</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2686,22 +2686,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129978642</v>
+        <v>129976353</v>
       </c>
       <c r="B22" t="n">
-        <v>83055</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2709,37 +2709,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574606</v>
+        <v>574636</v>
       </c>
       <c r="R22" t="n">
-        <v>6738867</v>
+        <v>6738816</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2783,12 +2783,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 55280-2025 artfynd.xlsx
+++ b/artfynd/A 55280-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129958743</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129976312</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,48 +892,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129978662</v>
+        <v>129976313</v>
       </c>
       <c r="B4" t="n">
-        <v>75196</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574596</v>
+        <v>574432</v>
       </c>
       <c r="R4" t="n">
-        <v>6738880</v>
+        <v>6738763</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +977,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129978658</v>
+        <v>129978662</v>
       </c>
       <c r="B5" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574591</v>
+        <v>574596</v>
       </c>
       <c r="R5" t="n">
-        <v>6738884</v>
+        <v>6738880</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,48 +1086,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129976313</v>
+        <v>129978658</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>75199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574432</v>
+        <v>574591</v>
       </c>
       <c r="R6" t="n">
-        <v>6738763</v>
+        <v>6738884</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,22 +1171,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129978665</v>
+        <v>129976308</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,37 +1194,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574442</v>
+        <v>574294</v>
       </c>
       <c r="R7" t="n">
-        <v>6738569</v>
+        <v>6738677</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,22 +1268,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129976308</v>
+        <v>129978665</v>
       </c>
       <c r="B8" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,37 +1291,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574294</v>
+        <v>574442</v>
       </c>
       <c r="R8" t="n">
-        <v>6738677</v>
+        <v>6738569</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1365,12 +1365,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1380,7 +1380,7 @@
         <v>129978657</v>
       </c>
       <c r="B9" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>129978682</v>
       </c>
       <c r="B10" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>129976309</v>
       </c>
       <c r="B11" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129978651</v>
+        <v>129978664</v>
       </c>
       <c r="B12" t="n">
-        <v>75196</v>
+        <v>90987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>5685</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574626</v>
+        <v>574298</v>
       </c>
       <c r="R12" t="n">
-        <v>6738882</v>
+        <v>6738745</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129978664</v>
+        <v>129978648</v>
       </c>
       <c r="B13" t="n">
-        <v>90984</v>
+        <v>98831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,34 +1793,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5685</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574298</v>
+        <v>574476</v>
       </c>
       <c r="R13" t="n">
-        <v>6738745</v>
+        <v>6738614</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1861,6 +1865,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1872,17 +1877,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129978648</v>
+        <v>129978651</v>
       </c>
       <c r="B14" t="n">
-        <v>98828</v>
+        <v>75199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,38 +1895,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219874</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574476</v>
+        <v>574626</v>
       </c>
       <c r="R14" t="n">
-        <v>6738614</v>
+        <v>6738882</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1962,7 +1963,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Lena Thommson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1984,7 +1984,7 @@
         <v>129976311</v>
       </c>
       <c r="B15" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,45 +2091,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129976350</v>
+        <v>129976307</v>
       </c>
       <c r="B16" t="n">
-        <v>75196</v>
+        <v>92925</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574629</v>
+        <v>574335</v>
       </c>
       <c r="R16" t="n">
-        <v>6738849</v>
+        <v>6738615</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2170,74 +2181,64 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129976307</v>
+        <v>129976350</v>
       </c>
       <c r="B17" t="n">
-        <v>92922</v>
+        <v>75199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574335</v>
+        <v>574629</v>
       </c>
       <c r="R17" t="n">
-        <v>6738615</v>
+        <v>6738849</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,51 +2279,50 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129978649</v>
+        <v>129978660</v>
       </c>
       <c r="B18" t="n">
-        <v>78841</v>
+        <v>75199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574294</v>
+        <v>574590</v>
       </c>
       <c r="R18" t="n">
-        <v>6738742</v>
+        <v>6738880</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2394,48 +2394,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129978660</v>
+        <v>129976348</v>
       </c>
       <c r="B19" t="n">
-        <v>75196</v>
+        <v>98797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574590</v>
+        <v>574433</v>
       </c>
       <c r="R19" t="n">
-        <v>6738880</v>
+        <v>6738720</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2473,78 +2485,67 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129976348</v>
+        <v>129978649</v>
       </c>
       <c r="B20" t="n">
-        <v>98794</v>
+        <v>78844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574433</v>
+        <v>574294</v>
       </c>
       <c r="R20" t="n">
-        <v>6738720</v>
+        <v>6738742</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2582,19 +2583,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
         <v>129978642</v>
       </c>
       <c r="B21" t="n">
-        <v>83055</v>
+        <v>83058</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>129976353</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>129978652</v>
       </c>
       <c r="B23" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>129978681</v>
       </c>
       <c r="B24" t="n">
-        <v>98711</v>
+        <v>98714</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,48 +3003,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129976315</v>
+        <v>129978653</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>75199</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574651</v>
+        <v>574629</v>
       </c>
       <c r="R25" t="n">
-        <v>6738821</v>
+        <v>6738896</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3088,60 +3088,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129978653</v>
+        <v>129976315</v>
       </c>
       <c r="B26" t="n">
-        <v>75196</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574629</v>
+        <v>574651</v>
       </c>
       <c r="R26" t="n">
-        <v>6738896</v>
+        <v>6738821</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3185,12 +3185,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3200,7 +3200,7 @@
         <v>129978646</v>
       </c>
       <c r="B27" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>129976310</v>
       </c>
       <c r="B28" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>129978641</v>
       </c>
       <c r="B29" t="n">
-        <v>83055</v>
+        <v>83058</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3501,32 +3501,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129978650</v>
+        <v>129978645</v>
       </c>
       <c r="B30" t="n">
-        <v>78841</v>
+        <v>98715</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574540</v>
+        <v>574565</v>
       </c>
       <c r="R30" t="n">
-        <v>6738742</v>
+        <v>6738840</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3598,32 +3598,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129978645</v>
+        <v>129978650</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>78844</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574565</v>
+        <v>574540</v>
       </c>
       <c r="R31" t="n">
-        <v>6738840</v>
+        <v>6738742</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3698,7 +3698,7 @@
         <v>129976317</v>
       </c>
       <c r="B32" t="n">
-        <v>78750</v>
+        <v>78753</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129976316</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3889,57 +3889,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129976349</v>
+        <v>129976351</v>
       </c>
       <c r="B34" t="n">
-        <v>98794</v>
+        <v>75199</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574623</v>
+        <v>574632</v>
       </c>
       <c r="R34" t="n">
-        <v>6738796</v>
+        <v>6738902</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3980,7 +3968,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3999,45 +3986,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129976351</v>
+        <v>129976349</v>
       </c>
       <c r="B35" t="n">
-        <v>75196</v>
+        <v>98797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574632</v>
+        <v>574623</v>
       </c>
       <c r="R35" t="n">
-        <v>6738902</v>
+        <v>6738796</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,6 +4077,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>129978643</v>
       </c>
       <c r="B36" t="n">
-        <v>83055</v>
+        <v>83058</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>129976314</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>129978654</v>
       </c>
       <c r="B38" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>129978656</v>
       </c>
       <c r="B39" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>129978663</v>
       </c>
       <c r="B40" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 55280-2025 artfynd.xlsx
+++ b/artfynd/A 55280-2025 artfynd.xlsx
@@ -782,57 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129976312</v>
+        <v>129976313</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574624</v>
+        <v>574432</v>
       </c>
       <c r="R3" t="n">
-        <v>6738804</v>
+        <v>6738763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,48 +879,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129976313</v>
+        <v>129978662</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>75199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574432</v>
+        <v>574596</v>
       </c>
       <c r="R4" t="n">
-        <v>6738763</v>
+        <v>6738880</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,19 +964,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129978662</v>
+        <v>129978658</v>
       </c>
       <c r="B5" t="n">
         <v>75199</v>
@@ -1024,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574596</v>
+        <v>574591</v>
       </c>
       <c r="R5" t="n">
-        <v>6738880</v>
+        <v>6738884</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,48 +1073,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129978658</v>
+        <v>129976312</v>
       </c>
       <c r="B6" t="n">
-        <v>75199</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574591</v>
+        <v>574624</v>
       </c>
       <c r="R6" t="n">
-        <v>6738884</v>
+        <v>6738804</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,18 +1164,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129978648</v>
+        <v>129978651</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>75199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,38 +1793,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574476</v>
+        <v>574626</v>
       </c>
       <c r="R13" t="n">
-        <v>6738614</v>
+        <v>6738882</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1865,7 +1861,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1877,55 +1872,67 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Lena Thommson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129978651</v>
+        <v>129976311</v>
       </c>
       <c r="B14" t="n">
-        <v>75199</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574626</v>
+        <v>574666</v>
       </c>
       <c r="R14" t="n">
-        <v>6738882</v>
+        <v>6738788</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,78 +1970,71 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129976311</v>
+        <v>129978648</v>
       </c>
       <c r="B15" t="n">
-        <v>98797</v>
+        <v>98831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574666</v>
+        <v>574476</v>
       </c>
       <c r="R15" t="n">
-        <v>6738788</v>
+        <v>6738614</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,12 +2079,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3294,60 +3294,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129976310</v>
+        <v>129978641</v>
       </c>
       <c r="B28" t="n">
-        <v>98797</v>
+        <v>83058</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574679</v>
+        <v>574386</v>
       </c>
       <c r="R28" t="n">
-        <v>6738793</v>
+        <v>6738787</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3385,67 +3373,78 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129978641</v>
+        <v>129976310</v>
       </c>
       <c r="B29" t="n">
-        <v>83058</v>
+        <v>98797</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574386</v>
+        <v>574679</v>
       </c>
       <c r="R29" t="n">
-        <v>6738787</v>
+        <v>6738793</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3483,18 +3482,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 55280-2025 artfynd.xlsx
+++ b/artfynd/A 55280-2025 artfynd.xlsx
@@ -782,45 +782,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129976313</v>
+        <v>129976312</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574432</v>
+        <v>574624</v>
       </c>
       <c r="R3" t="n">
-        <v>6738763</v>
+        <v>6738804</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +873,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1073,57 +1086,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129976312</v>
+        <v>129976313</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574624</v>
+        <v>574432</v>
       </c>
       <c r="R6" t="n">
-        <v>6738804</v>
+        <v>6738763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,7 +1165,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129978652</v>
+        <v>129978681</v>
       </c>
       <c r="B23" t="n">
-        <v>75199</v>
+        <v>98714</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2806,37 +2806,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574634</v>
+        <v>574342</v>
       </c>
       <c r="R23" t="n">
-        <v>6738899</v>
+        <v>6738765</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2866,28 +2863,17 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2906,10 +2892,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129978681</v>
+        <v>129978652</v>
       </c>
       <c r="B24" t="n">
-        <v>98714</v>
+        <v>75199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2917,34 +2903,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574342</v>
+        <v>574634</v>
       </c>
       <c r="R24" t="n">
-        <v>6738765</v>
+        <v>6738899</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2974,17 +2963,28 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3695,10 +3695,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129976317</v>
+        <v>129976316</v>
       </c>
       <c r="B32" t="n">
-        <v>78753</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,21 +3706,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574617</v>
+        <v>574581</v>
       </c>
       <c r="R32" t="n">
-        <v>6738757</v>
+        <v>6738833</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129976316</v>
+        <v>129976317</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>78753</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3803,21 +3803,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574581</v>
+        <v>574617</v>
       </c>
       <c r="R33" t="n">
-        <v>6738833</v>
+        <v>6738757</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 55280-2025 artfynd.xlsx
+++ b/artfynd/A 55280-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129958743</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,57 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129976312</v>
+        <v>129976313</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574624</v>
+        <v>574432</v>
       </c>
       <c r="R3" t="n">
-        <v>6738804</v>
+        <v>6738763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1086,45 +1073,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129976313</v>
+        <v>129976312</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574432</v>
+        <v>574624</v>
       </c>
       <c r="R6" t="n">
-        <v>6738763</v>
+        <v>6738804</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,6 +1164,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129976308</v>
+        <v>129978665</v>
       </c>
       <c r="B7" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,37 +1194,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574294</v>
+        <v>574442</v>
       </c>
       <c r="R7" t="n">
-        <v>6738677</v>
+        <v>6738569</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,22 +1268,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129978665</v>
+        <v>129976308</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,37 +1291,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574442</v>
+        <v>574294</v>
       </c>
       <c r="R8" t="n">
-        <v>6738569</v>
+        <v>6738677</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1365,12 +1365,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1477,7 +1477,7 @@
         <v>129978682</v>
       </c>
       <c r="B10" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>129976309</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129978664</v>
+        <v>129978651</v>
       </c>
       <c r="B12" t="n">
-        <v>90987</v>
+        <v>75199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5685</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574298</v>
+        <v>574626</v>
       </c>
       <c r="R12" t="n">
-        <v>6738745</v>
+        <v>6738882</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129978651</v>
+        <v>129978664</v>
       </c>
       <c r="B13" t="n">
-        <v>75199</v>
+        <v>90988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>5685</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574626</v>
+        <v>574298</v>
       </c>
       <c r="R13" t="n">
-        <v>6738882</v>
+        <v>6738745</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1882,7 +1882,7 @@
         <v>129976311</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>129978648</v>
       </c>
       <c r="B15" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>129976307</v>
       </c>
       <c r="B16" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,32 +2297,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129978660</v>
+        <v>129978649</v>
       </c>
       <c r="B18" t="n">
-        <v>75199</v>
+        <v>78845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574590</v>
+        <v>574294</v>
       </c>
       <c r="R18" t="n">
-        <v>6738880</v>
+        <v>6738742</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2394,60 +2394,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129976348</v>
+        <v>129978660</v>
       </c>
       <c r="B19" t="n">
-        <v>98797</v>
+        <v>75199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574433</v>
+        <v>574590</v>
       </c>
       <c r="R19" t="n">
-        <v>6738720</v>
+        <v>6738880</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2485,67 +2473,78 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129978649</v>
+        <v>129976348</v>
       </c>
       <c r="B20" t="n">
-        <v>78844</v>
+        <v>98798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574294</v>
+        <v>574433</v>
       </c>
       <c r="R20" t="n">
-        <v>6738742</v>
+        <v>6738720</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2583,18 +2582,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
         <v>129978642</v>
       </c>
       <c r="B21" t="n">
-        <v>83058</v>
+        <v>83059</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>129976353</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>129978681</v>
       </c>
       <c r="B23" t="n">
-        <v>98714</v>
+        <v>98715</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>129976315</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>129978646</v>
       </c>
       <c r="B27" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>129978641</v>
       </c>
       <c r="B28" t="n">
-        <v>83058</v>
+        <v>83059</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>129976310</v>
       </c>
       <c r="B29" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>129978645</v>
       </c>
       <c r="B30" t="n">
-        <v>98715</v>
+        <v>98716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>129978650</v>
       </c>
       <c r="B31" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3695,10 +3695,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129976316</v>
+        <v>129976317</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>78754</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,21 +3706,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574581</v>
+        <v>574617</v>
       </c>
       <c r="R32" t="n">
-        <v>6738833</v>
+        <v>6738757</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129976317</v>
+        <v>129976316</v>
       </c>
       <c r="B33" t="n">
-        <v>78753</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3803,21 +3803,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574617</v>
+        <v>574581</v>
       </c>
       <c r="R33" t="n">
-        <v>6738757</v>
+        <v>6738833</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3989,7 +3989,7 @@
         <v>129976349</v>
       </c>
       <c r="B35" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>129978643</v>
       </c>
       <c r="B36" t="n">
-        <v>83058</v>
+        <v>83059</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>129976314</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 55280-2025 artfynd.xlsx
+++ b/artfynd/A 55280-2025 artfynd.xlsx
@@ -3501,32 +3501,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129978645</v>
+        <v>129978650</v>
       </c>
       <c r="B30" t="n">
-        <v>98716</v>
+        <v>78845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223591</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574565</v>
+        <v>574540</v>
       </c>
       <c r="R30" t="n">
-        <v>6738840</v>
+        <v>6738742</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3598,32 +3598,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129978650</v>
+        <v>129978645</v>
       </c>
       <c r="B31" t="n">
-        <v>78845</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574540</v>
+        <v>574565</v>
       </c>
       <c r="R31" t="n">
-        <v>6738742</v>
+        <v>6738840</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>

--- a/artfynd/A 55280-2025 artfynd.xlsx
+++ b/artfynd/A 55280-2025 artfynd.xlsx
@@ -1879,60 +1879,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129976311</v>
+        <v>129978648</v>
       </c>
       <c r="B14" t="n">
-        <v>98798</v>
+        <v>98832</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574666</v>
+        <v>574476</v>
       </c>
       <c r="R14" t="n">
-        <v>6738788</v>
+        <v>6738614</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,64 +1969,72 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129978648</v>
+        <v>129976311</v>
       </c>
       <c r="B15" t="n">
-        <v>98832</v>
+        <v>98798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574476</v>
+        <v>574666</v>
       </c>
       <c r="R15" t="n">
-        <v>6738614</v>
+        <v>6738788</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,12 +2079,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Lena Thommson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3294,48 +3294,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129978641</v>
+        <v>129976310</v>
       </c>
       <c r="B28" t="n">
-        <v>83059</v>
+        <v>98798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574386</v>
+        <v>574679</v>
       </c>
       <c r="R28" t="n">
-        <v>6738787</v>
+        <v>6738793</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3373,78 +3385,67 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129976310</v>
+        <v>129978641</v>
       </c>
       <c r="B29" t="n">
-        <v>98798</v>
+        <v>83059</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574679</v>
+        <v>574386</v>
       </c>
       <c r="R29" t="n">
-        <v>6738793</v>
+        <v>6738787</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3482,51 +3483,50 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129978650</v>
+        <v>129978645</v>
       </c>
       <c r="B30" t="n">
-        <v>78845</v>
+        <v>98716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>223591</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574540</v>
+        <v>574565</v>
       </c>
       <c r="R30" t="n">
-        <v>6738742</v>
+        <v>6738840</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3598,32 +3598,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129978645</v>
+        <v>129978650</v>
       </c>
       <c r="B31" t="n">
-        <v>98716</v>
+        <v>78845</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574565</v>
+        <v>574540</v>
       </c>
       <c r="R31" t="n">
-        <v>6738840</v>
+        <v>6738742</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>

--- a/artfynd/A 55280-2025 artfynd.xlsx
+++ b/artfynd/A 55280-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129958743</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129976313</v>
+        <v>129978658</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>75200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574432</v>
+        <v>574591</v>
       </c>
       <c r="R3" t="n">
-        <v>6738763</v>
+        <v>6738884</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>129978662</v>
       </c>
       <c r="B4" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,48 +976,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129978658</v>
+        <v>129976313</v>
       </c>
       <c r="B5" t="n">
-        <v>75199</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574591</v>
+        <v>574432</v>
       </c>
       <c r="R5" t="n">
-        <v>6738884</v>
+        <v>6738763</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,12 +1061,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
         <v>129976312</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129978665</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>129976308</v>
       </c>
       <c r="B8" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>129978657</v>
       </c>
       <c r="B9" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>129978682</v>
       </c>
       <c r="B10" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>129976309</v>
       </c>
       <c r="B11" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129978651</v>
+        <v>129978664</v>
       </c>
       <c r="B12" t="n">
-        <v>75199</v>
+        <v>91005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>5685</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574626</v>
+        <v>574298</v>
       </c>
       <c r="R12" t="n">
-        <v>6738882</v>
+        <v>6738745</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129978664</v>
+        <v>129978651</v>
       </c>
       <c r="B13" t="n">
-        <v>90988</v>
+        <v>75200</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5685</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574298</v>
+        <v>574626</v>
       </c>
       <c r="R13" t="n">
-        <v>6738745</v>
+        <v>6738882</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1882,7 +1882,7 @@
         <v>129978648</v>
       </c>
       <c r="B14" t="n">
-        <v>98832</v>
+        <v>98849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129976311</v>
       </c>
       <c r="B15" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>129976307</v>
       </c>
       <c r="B16" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>129976350</v>
       </c>
       <c r="B17" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,48 +2297,60 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129978649</v>
+        <v>129976348</v>
       </c>
       <c r="B18" t="n">
-        <v>78845</v>
+        <v>98815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574294</v>
+        <v>574433</v>
       </c>
       <c r="R18" t="n">
-        <v>6738742</v>
+        <v>6738720</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2376,18 +2388,19 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2397,7 +2410,7 @@
         <v>129978660</v>
       </c>
       <c r="B19" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,60 +2504,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129976348</v>
+        <v>129978649</v>
       </c>
       <c r="B20" t="n">
-        <v>98798</v>
+        <v>78846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574433</v>
+        <v>574294</v>
       </c>
       <c r="R20" t="n">
-        <v>6738720</v>
+        <v>6738742</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2582,19 +2583,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
         <v>129978642</v>
       </c>
       <c r="B21" t="n">
-        <v>83059</v>
+        <v>83065</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>129976353</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>129978681</v>
       </c>
       <c r="B23" t="n">
-        <v>98715</v>
+        <v>98732</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>129978652</v>
       </c>
       <c r="B24" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>129978653</v>
       </c>
       <c r="B25" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>129976315</v>
       </c>
       <c r="B26" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>129978646</v>
       </c>
       <c r="B27" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,60 +3294,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129976310</v>
+        <v>129978641</v>
       </c>
       <c r="B28" t="n">
-        <v>98798</v>
+        <v>83065</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kitteln, Dlr</t>
+          <t>Sneåsen söder, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574679</v>
+        <v>574386</v>
       </c>
       <c r="R28" t="n">
-        <v>6738793</v>
+        <v>6738787</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3385,67 +3373,78 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129978641</v>
+        <v>129976310</v>
       </c>
       <c r="B29" t="n">
-        <v>83059</v>
+        <v>98815</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sneåsen söder, Dlr</t>
+          <t>Kitteln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574386</v>
+        <v>574679</v>
       </c>
       <c r="R29" t="n">
-        <v>6738787</v>
+        <v>6738793</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3483,50 +3482,51 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129978645</v>
+        <v>129978650</v>
       </c>
       <c r="B30" t="n">
-        <v>98716</v>
+        <v>78846</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223591</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574565</v>
+        <v>574540</v>
       </c>
       <c r="R30" t="n">
-        <v>6738840</v>
+        <v>6738742</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3598,32 +3598,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129978650</v>
+        <v>129978645</v>
       </c>
       <c r="B31" t="n">
-        <v>78845</v>
+        <v>98733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>223591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574540</v>
+        <v>574565</v>
       </c>
       <c r="R31" t="n">
-        <v>6738742</v>
+        <v>6738840</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3695,10 +3695,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129976317</v>
+        <v>129976316</v>
       </c>
       <c r="B32" t="n">
-        <v>78754</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,21 +3706,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574617</v>
+        <v>574581</v>
       </c>
       <c r="R32" t="n">
-        <v>6738757</v>
+        <v>6738833</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129976316</v>
+        <v>129976317</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>78755</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3803,21 +3803,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574581</v>
+        <v>574617</v>
       </c>
       <c r="R33" t="n">
-        <v>6738833</v>
+        <v>6738757</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
         <v>129976351</v>
       </c>
       <c r="B34" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>129976349</v>
       </c>
       <c r="B35" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>129978643</v>
       </c>
       <c r="B36" t="n">
-        <v>83059</v>
+        <v>83065</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>129976314</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>129978654</v>
       </c>
       <c r="B38" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>129978656</v>
       </c>
       <c r="B39" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>129978663</v>
       </c>
       <c r="B40" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
